--- a/Cosas que llegan de mercado/2026/Periodo 1/Nota3 (1).xlsx
+++ b/Cosas que llegan de mercado/2026/Periodo 1/Nota3 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\Cosas que llegan de mercado\2026\Periodo 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7109FE3-30AD-4FB0-9570-D6A41774C372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2217930-7E13-471B-9D8B-8AE17CABC0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
     <t>Cantidad</t>
   </si>
@@ -43,6 +43,12 @@
   </si>
   <si>
     <t>SI LLEGO TODO BIEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI LLEGO TODO BIEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI YA LLEGO </t>
   </si>
 </sst>
 </file>
@@ -628,6 +634,9 @@
         <f>J3*K3</f>
         <v>810</v>
       </c>
+      <c r="M3" t="s">
+        <v>6</v>
+      </c>
       <c r="N3">
         <f>SUM(L3:L68)</f>
         <v>2767</v>
@@ -636,7 +645,7 @@
     <row r="4" spans="10:14" x14ac:dyDescent="0.25">
       <c r="N4" s="1"/>
     </row>
-    <row r="19" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J19">
         <v>2</v>
       </c>
@@ -647,8 +656,11 @@
         <f>J19*K19</f>
         <v>206</v>
       </c>
+      <c r="M19" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J35">
         <v>3</v>
       </c>
@@ -658,6 +670,9 @@
       <c r="L35">
         <f>J35*K35</f>
         <v>402</v>
+      </c>
+      <c r="M35" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="10:13" x14ac:dyDescent="0.25">
@@ -675,7 +690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J66">
         <v>2</v>
       </c>
@@ -685,6 +700,9 @@
       <c r="L66">
         <f>J66*K66</f>
         <v>596</v>
+      </c>
+      <c r="M66" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
